--- a/planilhas/subvencao-petrobras.xlsx
+++ b/planilhas/subvencao-petrobras.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -607,121 +607,121 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>e para a gasolina ela passa despercebida; para o diesel ela estoura. Pelo nosso cálculo o diesel renderia</t>
+          <t>e na gasolina ela passa despercebida: R$ 882 milhões por mês cabe no orçamento. No diesel ela quebra.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>R$ 14 bilhões em três meses, e a MP 1.395, de 9/10/2026, abriu crédito de R$ 7,5 bilhões para o programa</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>inteiro. Ou seja, a subvenção não é paga em cada litro: há limite orçamentário, e provavelmente limite</t>
+          <t>Pela nossa conta o diesel renderia R$ 14 bilhões em três meses, só para a Petrobras. Três coisas dizem</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>de volume por empresa que não está nesta planilha.</t>
+          <t>que isso é muito:</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. A subvenção é do diesel A RODOVIÁRIO, e o denominador aqui é a produção total de diesel, que</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Leia a linha do ganho como TETO: é quanto a medida valeria se alcançasse tudo. O que de fato foi pago</t>
+          <t xml:space="preserve">     inclui marítimo, não rodoviário e outros usos.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sai no resultado da empresa e na execução orçamentária, não aqui.</t>
+          <t xml:space="preserve">  2. Os créditos extraordinários de 2026 para subvenção de combustíveis somam cerca de R$ 17 bilhões</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (MP 1.388 com R$ 3,15 bi, MP 1.389 com R$ 6,6 bi, MP 1.395 com R$ 7,52 bi), e a fatia do diesel</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>E O DESCONTO NEM SEMPRE É A SUBVENÇÃO</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     rodoviário fica perto de R$ 9 bilhões — para todas as empresas e um período maior.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A diferença entre as duas colunas de preço é o desconto que a empresa de fato aplicou. Quando ela mexe</t>
+          <t xml:space="preserve">  3. Desde a MP 1.391 o valor por litro é definido por ato do Ministro da Fazenda, em janelas de 30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>na tabela no mesmo dia em que a subvenção entra, os dois deixam de coincidir. Na gasolina coincidem:</t>
+          <t xml:space="preserve">     dias renováveis. Não é R$ 2,12 correndo sem parar.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>a média sai em R$ 0,4400, que é o valor legal. No diesel a média sai acima de R$ 1,12 porque em 2/6/2026</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a Petrobras subiu a tabela junto.</t>
+          <t>O FUNDO DA QUESTÃO: são duas coisas diferentes. O DESCONTO que a Petrobras dá no preço à distribuidora</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>está na tabela dela e é o que esta planilha mede. O que o TESOURO devolve a ela não está em lugar</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>O QUE ISTO NÃO É</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>nenhum público. A T.3 supõe que os dois são iguais; se o Tesouro ressarce menos que o desconto, a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Não é resultado contábil. Ignora custo de produção, tributo, hedge, estoque e preço de exportação.</t>
+          <t>diferença não é ganho, é prejuízo.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Mede uma coisa só: a diferença entre vender ao preço de tabela e vender ao preço com subvenção, no</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>volume que a empresa de fato produziu e importou.</t>
+          <t>Leia a linha do ganho como TETO: quanto a medida valeria se alcançasse tudo. O que de fato foi pago</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E não desconta o que a subvenção custa ao Tesouro, que é o outro lado da mesma moeda.</t>
+          <t>sai no resultado da empresa e na execução orçamentária, não aqui.</t>
         </is>
       </c>
     </row>
@@ -731,50 +731,126 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>ATENÇÃO AO DIESEL</t>
+          <t>E O DESCONTO NEM SEMPRE É A SUBVENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>O PPI da ANP para diesel é de Diesel A S10, então a linha do prejuízo com importações compara o S-10</t>
+          <t>A diferença entre as duas colunas de preço é o desconto que a empresa de fato aplicou. Quando ela mexe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>com o PPI do S-10. Já a produção e a importação são de diesel TOTAL, porque nem a ANP nem o Relatório</t>
+          <t>na tabela no mesmo dia em que a subvenção entra, os dois deixam de coincidir. Na gasolina coincidem:</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>de Desembaraços separam por teor de enxofre. Como a subvenção é a mesma para S-10 e S-500 (R$ 1,12 e</t>
+          <t>a média sai em R$ 0,4400, que é o valor legal. No diesel a média sai acima de R$ 1,12 porque em 2/6/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>depois R$ 2,12 por litro nas duas), a linha do ganho não sofre com isso; a do prejuízo sofre um pouco,</t>
+          <t>a Petrobras subiu a tabela junto.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>porque o S-500 é 28% das vendas e custa alguns centavos menos.</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>O QUE ISTO NÃO É</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
+        <is>
+          <t>Não é resultado contábil. Ignora custo de produção, tributo, hedge, estoque e preço de exportação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Mede uma coisa só: a diferença entre vender ao preço de tabela e vender ao preço com subvenção, no</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>volume que a empresa de fato produziu e importou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>E não desconta o que a subvenção custa ao Tesouro, que é o outro lado da mesma moeda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ATENÇÃO AO DIESEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>O PPI da ANP para diesel é de Diesel A S10, então a linha do prejuízo com importações compara o S-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>com o PPI do S-10. Já a produção e a importação são de diesel TOTAL, porque nem a ANP nem o Relatório</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>de Desembaraços separam por teor de enxofre. Como a subvenção é a mesma para S-10 e S-500 (R$ 1,12 e</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>depois R$ 2,12 por litro nas duas), a linha do ganho não sofre com isso; a do prejuízo sofre um pouco,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>porque o S-500 é 28% das vendas e custa alguns centavos menos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Fontes: ANP (produção, desembaraços, PPI) e tabelas de preços da Petrobras (Resolução ANP 795/2019).</t>
         </is>
